--- a/data/trans_camb/KIDM_A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 2,79</t>
+          <t>-8,87; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 11,26</t>
+          <t>-6,06; 11,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,86; -1,42</t>
+          <t>-11,88; -1,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,73</t>
+          <t>0,0; 10,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,69</t>
+          <t>0,0; 30,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,79</t>
+          <t>-3,94; 2,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,2</t>
+          <t>-2,67; 6,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 19,22</t>
+          <t>-2,27; 16,23</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,03</t>
+          <t>-1,15; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,17</t>
+          <t>-2,81; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,87</t>
+          <t>-2,7; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,11</t>
+          <t>0,53; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,64</t>
+          <t>-2,99; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,73</t>
+          <t>-2,97; 0,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,35</t>
+          <t>0,15; 4,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,45</t>
+          <t>-2,46; 0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,69</t>
+          <t>-2,38; 0,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 472,2</t>
+          <t>-58,56; 480,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,27; 247,08</t>
+          <t>-85,27; 197,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 298,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 663,14</t>
+          <t>2,33; 641,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,44</t>
+          <t>-100,0; 168,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 382,8</t>
+          <t>0,48; 340,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,1; 54,02</t>
+          <t>-83,11; 46,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 94,98</t>
+          <t>-83,9; 63,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 8,0</t>
+          <t>-2,66; 8,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,86</t>
+          <t>-5,46; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,3</t>
+          <t>-2,73; 5,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 0,0</t>
+          <t>-9,11; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 6,4</t>
+          <t>-4,38; 6,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,0</t>
+          <t>-9,9; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,08</t>
+          <t>-3,38; 2,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,52</t>
+          <t>-3,14; 3,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,64</t>
+          <t>-4,96; 0,67</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,81; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,4</t>
+          <t>-1,15; 3,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,09</t>
+          <t>-2,56; 1,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,02</t>
+          <t>-2,67; 1,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,19</t>
+          <t>-0,22; 3,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,78</t>
+          <t>-2,01; 1,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,24</t>
+          <t>-2,49; 1,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,07</t>
+          <t>-0,36; 2,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,94</t>
+          <t>-1,65; 0,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,49</t>
+          <t>-1,92; 0,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 264,52</t>
+          <t>-42,2; 280,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 113,65</t>
+          <t>-74,92; 100,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 93,39</t>
+          <t>-88,86; 122,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 420,69</t>
+          <t>-20,01; 369,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 220,32</t>
+          <t>-74,79; 189,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 183,21</t>
+          <t>-86,81; 121,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 215,25</t>
+          <t>-14,0; 210,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 83,19</t>
+          <t>-60,39; 56,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 39,03</t>
+          <t>-75,98; 49,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 4,05</t>
+          <t>-8,98; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 11,37</t>
+          <t>-6,18; 11,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -1,42</t>
+          <t>-12,04; -1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 10,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,53</t>
+          <t>0,0; 32,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,76</t>
+          <t>-3,96; 2,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 6,85</t>
+          <t>-2,35; 7,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 16,23</t>
+          <t>-2,25; 17,24</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 573,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,14</t>
+          <t>-1,41; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,17</t>
+          <t>-2,65; 1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,94</t>
+          <t>-2,68; 1,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,04</t>
+          <t>0,37; 6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,57</t>
+          <t>-3,32; 0,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,71</t>
+          <t>-2,93; 0,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,19</t>
+          <t>0,42; 4,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,36</t>
+          <t>-2,36; 0,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,47</t>
+          <t>-2,42; 0,46</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 480,56</t>
+          <t>-56,94; 444,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,27; 197,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 298,43</t>
+          <t>-100,0; 326,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 641,45</t>
+          <t>-4,7; 622,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 168,24</t>
+          <t>-97,07; 118,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 340,65</t>
+          <t>2,41; 361,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,11; 46,32</t>
+          <t>-82,51; 43,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,9; 63,05</t>
+          <t>-86,95; 49,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 8,15</t>
+          <t>-1,47; 9,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,89</t>
+          <t>-5,42; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,02</t>
+          <t>-2,76; 6,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 0,0</t>
+          <t>-9,93; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 6,83</t>
+          <t>-4,58; 6,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 0,0</t>
+          <t>-10,19; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,88</t>
+          <t>-3,54; 3,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,58</t>
+          <t>-2,83; 3,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,67</t>
+          <t>-5,42; 0,68</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,81; —</t>
+          <t>-84,53; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,3</t>
+          <t>-1,03; 3,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,04</t>
+          <t>-2,4; 1,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,22</t>
+          <t>-2,77; 1,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,89</t>
+          <t>-0,22; 3,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,77</t>
+          <t>-1,9; 1,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,12</t>
+          <t>-2,25; 1,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,82</t>
+          <t>-0,08; 2,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,77</t>
+          <t>-1,68; 0,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,57</t>
+          <t>-2,02; 0,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 280,88</t>
+          <t>-41,45; 287,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 100,41</t>
+          <t>-74,76; 133,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 122,43</t>
+          <t>-89,07; 125,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 369,77</t>
+          <t>-19,03; 373,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 189,86</t>
+          <t>-72,48; 189,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,81; 121,92</t>
+          <t>-86,14; 146,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 210,43</t>
+          <t>-2,95; 227,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 56,47</t>
+          <t>-60,27; 65,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 49,9</t>
+          <t>-76,49; 58,66</t>
         </is>
       </c>
     </row>
